--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.44916737838148</v>
+        <v>3.810489698986991</v>
       </c>
       <c r="D2" t="n">
-        <v>23.32980852814409</v>
+        <v>3.791093885823415</v>
       </c>
       <c r="E2" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F2" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.69904813108709</v>
+        <v>4.013595321301652</v>
       </c>
       <c r="D3" t="n">
-        <v>24.68194117929681</v>
+        <v>4.010815441635732</v>
       </c>
       <c r="E3" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F3" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.74625356829073</v>
+        <v>1.746266204847244</v>
       </c>
       <c r="D4" t="n">
-        <v>10.83219338735733</v>
+        <v>1.760231425445567</v>
       </c>
       <c r="E4" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F4" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.07733108109365</v>
+        <v>2.775066300677719</v>
       </c>
       <c r="D5" t="n">
-        <v>17.29951196198399</v>
+        <v>2.811170693822398</v>
       </c>
       <c r="E5" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F5" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.28063103323472</v>
+        <v>2.808102542900643</v>
       </c>
       <c r="D6" t="n">
-        <v>15.81363033511837</v>
+        <v>2.569714929456735</v>
       </c>
       <c r="E6" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F6" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.08129805974713</v>
+        <v>5.375710934708909</v>
       </c>
       <c r="D7" t="n">
-        <v>33.19182962450237</v>
+        <v>5.393672313981635</v>
       </c>
       <c r="E7" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F7" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.38547461192551</v>
+        <v>4.937639624437896</v>
       </c>
       <c r="D8" t="n">
-        <v>30.36549347284632</v>
+        <v>4.934392689337527</v>
       </c>
       <c r="E8" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F8" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.2011130456239</v>
+        <v>2.470180869913884</v>
       </c>
       <c r="D9" t="n">
-        <v>15.21702565642857</v>
+        <v>2.472766669169643</v>
       </c>
       <c r="E9" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F9" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.23930632155777</v>
+        <v>2.151387277253137</v>
       </c>
       <c r="D10" t="n">
-        <v>13.14311434916641</v>
+        <v>2.135756081739542</v>
       </c>
       <c r="E10" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F10" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.30931551823362</v>
+        <v>5.250263771712963</v>
       </c>
       <c r="D11" t="n">
-        <v>32.31190383239974</v>
+        <v>5.250684372764957</v>
       </c>
       <c r="E11" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F11" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.15436995364882</v>
+        <v>5.875085117467933</v>
       </c>
       <c r="D12" t="n">
-        <v>36.09464480932455</v>
+        <v>5.865379781515239</v>
       </c>
       <c r="E12" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F12" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.661805463570616</v>
+        <v>1.570043387830225</v>
       </c>
       <c r="D13" t="n">
-        <v>9.989999759457048</v>
+        <v>1.62337496091177</v>
       </c>
       <c r="E13" t="n">
-        <v>8.93233577264766</v>
+        <v>1.451504563055245</v>
       </c>
       <c r="F13" t="n">
-        <v>8.95695234396835</v>
+        <v>1.455504755894857</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
